--- a/Models/Молоко/results/Молоко - Лучшие модели.xlsx
+++ b/Models/Молоко/results/Молоко - Лучшие модели.xlsx
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.119999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="C2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>21.34</v>
+        <v>19.57</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -483,17 +483,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.9</v>
+        <v>9.94</v>
       </c>
       <c r="C3" t="n">
-        <v>8.220000000000001</v>
+        <v>11.12</v>
       </c>
       <c r="D3" t="n">
-        <v>19.02</v>
+        <v>22.16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -504,17 +504,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.73</v>
+        <v>10.77</v>
       </c>
       <c r="C4" t="n">
-        <v>16.55</v>
+        <v>9.92</v>
       </c>
       <c r="D4" t="n">
-        <v>39.35</v>
+        <v>25.56</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.65</v>
+        <v>7.5</v>
       </c>
       <c r="C5" t="n">
-        <v>10.06</v>
+        <v>10.91</v>
       </c>
       <c r="D5" t="n">
-        <v>27.55</v>
+        <v>27.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SARIMA</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.9</v>
+        <v>15.77</v>
       </c>
       <c r="C6" t="n">
-        <v>16.93</v>
+        <v>13.2</v>
       </c>
       <c r="D6" t="n">
-        <v>41.14</v>
+        <v>33.76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68.94</v>
+        <v>63.09</v>
       </c>
       <c r="C7" t="n">
-        <v>104.99</v>
+        <v>81.36</v>
       </c>
       <c r="D7" t="n">
-        <v>37.92</v>
+        <v>54.61</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.25</v>
+        <v>33.75</v>
       </c>
       <c r="C8" t="n">
-        <v>12.35</v>
+        <v>29.05</v>
       </c>
       <c r="D8" t="n">
-        <v>65.70999999999999</v>
+        <v>121.66</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.83</v>
+        <v>10.45</v>
       </c>
       <c r="C9" t="n">
-        <v>8.449999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="D9" t="n">
-        <v>12.39</v>
+        <v>18.57</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.73</v>
+        <v>3.46</v>
       </c>
       <c r="C10" t="n">
-        <v>5.5</v>
+        <v>5.17</v>
       </c>
       <c r="D10" t="n">
-        <v>14.85</v>
+        <v>12.86</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -651,17 +651,17 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7.89</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>9.18</v>
+        <v>10.33</v>
       </c>
       <c r="D11" t="n">
-        <v>7.72</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.94</v>
+        <v>4.43</v>
       </c>
       <c r="C12" t="n">
-        <v>6.69</v>
+        <v>4.64</v>
       </c>
       <c r="D12" t="n">
-        <v>30.88</v>
+        <v>22.41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -693,17 +693,17 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.07</v>
+        <v>10.53</v>
       </c>
       <c r="C13" t="n">
-        <v>11.37</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>21.97</v>
+        <v>24.89</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.77</v>
+        <v>11.89</v>
       </c>
       <c r="C14" t="n">
-        <v>13.48</v>
+        <v>27.65</v>
       </c>
       <c r="D14" t="n">
-        <v>11.75</v>
+        <v>17.88</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>HW</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1.79979758155598e+17</v>
+        <v>206.67</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
@@ -752,17 +752,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.8</v>
+        <v>8.68</v>
       </c>
       <c r="C16" t="n">
-        <v>17.57</v>
+        <v>1.53</v>
       </c>
       <c r="D16" t="n">
-        <v>54.33</v>
+        <v>48.84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -773,17 +773,17 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.46</v>
+        <v>5.64</v>
       </c>
       <c r="C17" t="n">
-        <v>12.86</v>
+        <v>1.67</v>
       </c>
       <c r="D17" t="n">
-        <v>30.42</v>
+        <v>17.73</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.54</v>
+        <v>12.33</v>
       </c>
       <c r="C18" t="n">
-        <v>46.78</v>
+        <v>15.61</v>
       </c>
       <c r="D18" t="n">
-        <v>69.81</v>
+        <v>46.63</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13.87</v>
+        <v>16.86</v>
       </c>
       <c r="C19" t="n">
-        <v>13.64</v>
+        <v>16.39</v>
       </c>
       <c r="D19" t="n">
-        <v>16.56</v>
+        <v>25.29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15.95</v>
+        <v>18.55</v>
       </c>
       <c r="C20" t="n">
-        <v>19.24</v>
+        <v>13.54</v>
       </c>
       <c r="D20" t="n">
-        <v>16.76</v>
+        <v>23.96</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>SARIMA</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.01</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>8.81</v>
+        <v>11.39</v>
       </c>
       <c r="D21" t="n">
-        <v>17.52</v>
+        <v>8.23</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HW</t>
+          <t>Prophet</t>
         </is>
       </c>
     </row>
